--- a/dados_auxiliares/procv_elemento.xlsx
+++ b/dados_auxiliares/procv_elemento.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x526325\OneDrive - rede.sp\painel orçamentário\python\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE92153-456C-452A-87F0-F67952AB3110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>num_elemento</t>
   </si>
@@ -57,9 +51,6 @@
     <t>Contratação PJ com Fins Lucrativos</t>
   </si>
   <si>
-    <t>Serv. de Tec. da Inf. e Com - PJ</t>
-  </si>
-  <si>
     <t>Auxílio - Alimentação</t>
   </si>
   <si>
@@ -109,13 +100,19 @@
   </si>
   <si>
     <t>Aquisição de Imóveis</t>
+  </si>
+  <si>
+    <t>Serviços de Tecnologia da Informação e Comunicação - PJ</t>
+  </si>
+  <si>
+    <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,7 +238,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -276,7 +273,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -453,29 +450,29 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
         <v>31901100</v>
       </c>
@@ -483,7 +480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
         <v>33503900</v>
       </c>
@@ -491,7 +488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
         <v>33901400</v>
       </c>
@@ -499,7 +496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
         <v>33903000</v>
       </c>
@@ -507,7 +504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
         <v>33903100</v>
       </c>
@@ -515,7 +512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
         <v>33903300</v>
       </c>
@@ -523,7 +520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
         <v>33903600</v>
       </c>
@@ -531,7 +528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
         <v>33903700</v>
       </c>
@@ -539,7 +536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
         <v>33903900</v>
       </c>
@@ -547,167 +544,168 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
         <v>33904000</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2">
         <v>33904600</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="2">
         <v>33904700</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="2">
         <v>33904800</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2">
         <v>33904900</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="2">
         <v>44905200</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="2">
         <v>33804100</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="2">
         <v>31909400</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="2">
         <v>33903500</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2">
         <v>33903500</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="2">
         <v>44905100</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="2">
         <v>44904000</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="2">
         <v>44803500</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="2">
         <v>44903900</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="2">
         <v>33909200</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="2">
         <v>33909300</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2">
         <v>33903200</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="2">
         <v>33913900</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="2">
         <v>44903500</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="2">
         <v>44906100</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>